--- a/mad-map-data-v2.xlsx
+++ b/mad-map-data-v2.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" tabRatio="600" firstSheet="0" activeTab="7" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_Lectura" sheetId="1" state="visible" r:id="rId1"/>
@@ -26,13 +26,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_Proximidad_Tematica" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames>
+    <definedName name="AreaNombres">OFFSET('03_Areas'!$B$5,0,0,COUNTA('03_Areas'!$B$5:$B$10000),1)</definedName>
+    <definedName name="InvestigadorNombres">OFFSET('07_Investigadores'!$B$5,0,0,COUNTA('07_Investigadores'!$B$5:$B$10000),1)</definedName>
+    <definedName name="LabNombres">OFFSET('06_Laboratorios'!$B$3,0,0,COUNTA('06_Laboratorios'!$B$3:$B$10000),1)</definedName>
     <definedName name="LineaNombres">OFFSET('01_Lineas'!$B$5,0,0,COUNTA('01_Lineas'!$B$5:$B$10000),1)</definedName>
-    <definedName name="SublineaNombres">OFFSET('02_Sublineas'!$B$5,0,0,COUNTA('02_Sublineas'!$B$5:$B$10000),1)</definedName>
-    <definedName name="AreaNombres">OFFSET('03_Areas'!$B$5,0,0,COUNTA('03_Areas'!$B$5:$B$10000),1)</definedName>
     <definedName name="ModoNombres">OFFSET('04_Modos'!$B$3,0,0,COUNTA('04_Modos'!$B$3:$B$10000),1)</definedName>
     <definedName name="SalidaNombres">OFFSET('05_Salidas'!$B$5,0,0,COUNTA('05_Salidas'!$B$5:$B$10000),1)</definedName>
-    <definedName name="LabNombres">OFFSET('06_Laboratorios'!$B$3,0,0,COUNTA('06_Laboratorios'!$B$3:$B$10000),1)</definedName>
-    <definedName name="InvestigadorNombres">OFFSET('07_Investigadores'!$B$5,0,0,COUNTA('07_Investigadores'!$B$5:$B$10000),1)</definedName>
+    <definedName name="SublineaNombres">OFFSET('02_Sublineas'!$B$5,0,0,COUNTA('02_Sublineas'!$B$5:$B$10000),1)</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'18_Proximidad_Tematica'!$A$4:$G$90</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -54,44 +54,52 @@
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <b val="1"/>
       <color rgb="FF111827"/>
       <sz val="18"/>
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <i val="1"/>
       <color rgb="FF6B7280"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <b val="1"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <b val="1"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <b val="1"/>
       <color rgb="FF111827"/>
       <sz val="14"/>
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <sz val="10"/>
     </font>
     <font>
@@ -109,8 +117,9 @@
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <i val="1"/>
-      <color rgb="00666666"/>
+      <color rgb="FF666666"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -143,7 +152,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EEEEEE"/>
+        <fgColor rgb="FFEEEEEE"/>
       </patternFill>
     </fill>
   </fills>
@@ -172,24 +181,25 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="FFCCCCCC"/>
       </left>
       <right style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="FFCCCCCC"/>
       </right>
       <top style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="FFCCCCCC"/>
       </top>
       <bottom style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="FFCCCCCC"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -232,22 +242,23 @@
     <xf numFmtId="2" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -617,11 +628,11 @@
   <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" style="21" min="1" max="1"/>
-    <col width="110" customWidth="1" style="21" min="2" max="2"/>
+    <col width="30" customWidth="1" style="24" min="1" max="1"/>
+    <col width="110" customWidth="1" style="24" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23" customHeight="1" s="21">
+    <row r="1" ht="23" customHeight="1" s="24">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>MAD-map · Estructura de datos v2</t>
@@ -629,14 +640,15 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="22" t="inlineStr">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t>Régimen sin áreas-MAD: Líneas troncales sostenidas por Laboratorios + sublíneas + temas.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="16" customHeight="1" s="21">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="3"/>
+    <row r="4" ht="16" customHeight="1" s="24">
+      <c r="A4" s="26" t="inlineStr">
         <is>
           <t>Modelo relacional</t>
         </is>
@@ -738,8 +750,9 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="16" customHeight="1" s="21">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="13"/>
+    <row r="14" ht="16" customHeight="1" s="24">
+      <c r="A14" s="26" t="inlineStr">
         <is>
           <t>Convenciones</t>
         </is>
@@ -789,7 +802,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>M:N (un Tema puede colgar de varias Sublíneas). Editar en la hoja 09_Sublinea_Tema.</t>
+          <t>M:N (un Tema puede colgar de varias Sublíneas). Editar en la hoja 08_Temas (cada fila atribuye un tema a una sublínea y un investigador).</t>
         </is>
       </c>
     </row>
@@ -831,24 +844,23 @@
   <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" style="21" min="1" max="2"/>
+    <col width="14" customWidth="1" style="24" min="1" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="21">
-      <c r="A1" s="20" t="inlineStr">
+    <row r="1" ht="18" customHeight="1" s="24">
+      <c r="A1" s="25" t="inlineStr">
         <is>
           <t>10 · Laboratorio ↔ Línea (m:n)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="22" t="inlineStr">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t>Un Lab sostiene una o varias Líneas. BORRADOR.</t>
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
@@ -861,7 +873,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="60" customHeight="1" s="24">
       <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Núcleo de Accesibilidad e Inclusión</t>
@@ -873,7 +885,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="60" customHeight="1" s="24">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Aconcagua Fablab</t>
@@ -885,7 +897,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="60" customHeight="1" s="24">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Aconcagua Fablab</t>
@@ -897,7 +909,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="60" customHeight="1" s="24">
       <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Personas y territorios</t>
@@ -909,7 +921,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="60" customHeight="1" s="24">
       <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Urbanismo afectivo</t>
@@ -921,7 +933,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="60" customHeight="1" s="24">
       <c r="A10" s="8" t="inlineStr">
         <is>
           <t>Patrimonio moderno</t>
@@ -940,10 +952,10 @@
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="A5:A505" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Nombre no válido" error="El valor debe coincidir con un nombre existente en la hoja correspondiente. Usa el menú desplegable para elegir uno." type="list">
-      <formula1>=LabNombres</formula1>
+      <formula1>LabNombres</formula1>
     </dataValidation>
     <dataValidation sqref="B5:B505" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Nombre no válido" error="El valor debe coincidir con un nombre existente en la hoja correspondiente. Usa el menú desplegable para elegir uno." type="list">
-      <formula1>=LineaNombres</formula1>
+      <formula1>LineaNombres</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -959,24 +971,24 @@
   <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" style="21" min="1" max="2"/>
+    <col width="24" customWidth="1" style="24" min="1" max="1"/>
+    <col width="27" customWidth="1" style="24" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="21">
-      <c r="A1" s="20" t="inlineStr">
+    <row r="1" ht="18" customHeight="1" s="24">
+      <c r="A1" s="25" t="inlineStr">
         <is>
           <t>11 · Laboratorio ↔ Salida (m:n)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="22" t="inlineStr">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t>Los Labs operacionalizan las Salidas. BORRADOR.</t>
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
@@ -989,7 +1001,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="30" customHeight="1" s="24">
       <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Núcleo de Accesibilidad e Inclusión</t>
@@ -997,11 +1009,11 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>Estado</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
+          <t>Industria</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="45" customHeight="1" s="24">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Núcleo de Accesibilidad e Inclusión</t>
@@ -1013,7 +1025,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="30" customHeight="1" s="24">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Aconcagua Fablab</t>
@@ -1025,7 +1037,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="30" customHeight="1" s="24">
       <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Aconcagua Fablab</t>
@@ -1049,7 +1061,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="30" customHeight="1" s="24">
       <c r="A10" s="8" t="inlineStr">
         <is>
           <t>Personas y territorios</t>
@@ -1061,7 +1073,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="30" customHeight="1" s="24">
       <c r="A11" s="8" t="inlineStr">
         <is>
           <t>Patrimonio moderno</t>
@@ -1073,7 +1085,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="30" customHeight="1" s="24">
       <c r="A12" s="8" t="inlineStr">
         <is>
           <t>Urbanismo afectivo</t>
@@ -1085,7 +1097,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="30" customHeight="1" s="24">
       <c r="A13" s="8" t="inlineStr">
         <is>
           <t>Urbanismo afectivo</t>
@@ -1104,10 +1116,10 @@
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="A5:A505" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Nombre no válido" error="El valor debe coincidir con un nombre existente en la hoja correspondiente. Usa el menú desplegable para elegir uno." type="list">
-      <formula1>=LabNombres</formula1>
+      <formula1>LabNombres</formula1>
     </dataValidation>
     <dataValidation sqref="B5:B505" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Nombre no válido" error="El valor debe coincidir con un nombre existente en la hoja correspondiente. Usa el menú desplegable para elegir uno." type="list">
-      <formula1>=SalidaNombres</formula1>
+      <formula1>SalidaNombres</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1123,25 +1135,24 @@
   <dimension ref="A1:B34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" style="21" min="1" max="1"/>
-    <col width="14" customWidth="1" style="21" min="2" max="2"/>
+    <col width="35.6640625" customWidth="1" style="24" min="1" max="1"/>
+    <col width="44.6640625" customWidth="1" style="24" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="21">
-      <c r="A1" s="20" t="inlineStr">
+    <row r="1" ht="18" customHeight="1" s="24">
+      <c r="A1" s="25" t="inlineStr">
         <is>
           <t>12 · Investigador ↔ Laboratorio (m:n)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="22" t="inlineStr">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t>Lectura desde el material. BORRADOR — algunos investigadores podrían estar en más laboratorios de los registrados aquí.</t>
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
@@ -1154,7 +1165,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="19" customHeight="1" s="24">
       <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Ursula Exss Cid</t>
@@ -1166,7 +1177,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="19" customHeight="1" s="24">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Katherine Exss Cid</t>
@@ -1178,7 +1189,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="19" customHeight="1" s="24">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Katherine Exss Cid</t>
@@ -1190,7 +1201,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="19" customHeight="1" s="24">
       <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Jorge Ferrada Herrera</t>
@@ -1202,7 +1213,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="19" customHeight="1" s="24">
       <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Jorge Ferrada Herrera</t>
@@ -1214,7 +1225,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="19" customHeight="1" s="24">
       <c r="A10" s="8" t="inlineStr">
         <is>
           <t>Andrés Garcés Alzamora</t>
@@ -1226,7 +1237,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="19" customHeight="1" s="24">
       <c r="A11" s="8" t="inlineStr">
         <is>
           <t>Andrés Garcés Alzamora</t>
@@ -1238,7 +1249,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="19" customHeight="1" s="24">
       <c r="A12" s="8" t="inlineStr">
         <is>
           <t>Iván Ivelic Yanes</t>
@@ -1250,7 +1261,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="19" customHeight="1" s="24">
       <c r="A13" s="8" t="inlineStr">
         <is>
           <t>David Luza Cornejo</t>
@@ -1262,7 +1273,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="19" customHeight="1" s="24">
       <c r="A14" s="8" t="inlineStr">
         <is>
           <t>David Luza Cornejo</t>
@@ -1274,7 +1285,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="19" customHeight="1" s="24">
       <c r="A15" s="8" t="inlineStr">
         <is>
           <t>Adriana Marín Toro</t>
@@ -1286,7 +1297,7 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="19" customHeight="1" s="24">
       <c r="A16" s="8" t="inlineStr">
         <is>
           <t>Álvaro Mercado Jara</t>
@@ -1298,7 +1309,7 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="19" customHeight="1" s="24">
       <c r="A17" s="8" t="inlineStr">
         <is>
           <t>Álvaro Mercado Jara</t>
@@ -1310,7 +1321,7 @@
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="19" customHeight="1" s="24">
       <c r="A18" s="8" t="inlineStr">
         <is>
           <t>Jaime Reyes Gil</t>
@@ -1322,7 +1333,7 @@
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="19" customHeight="1" s="24">
       <c r="A19" s="8" t="inlineStr">
         <is>
           <t>Rodrigo Saavedra Venegas</t>
@@ -1334,7 +1345,7 @@
         </is>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="19" customHeight="1" s="24">
       <c r="A20" s="8" t="inlineStr">
         <is>
           <t>Daniela Salgado Cofré</t>
@@ -1346,7 +1357,7 @@
         </is>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="19" customHeight="1" s="24">
       <c r="A21" s="8" t="inlineStr">
         <is>
           <t>Daniela Salgado Cofré</t>
@@ -1358,7 +1369,7 @@
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="19" customHeight="1" s="24">
       <c r="A22" s="8" t="inlineStr">
         <is>
           <t>Herbert Spencer González</t>
@@ -1370,7 +1381,7 @@
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="19" customHeight="1" s="24">
       <c r="A23" s="8" t="inlineStr">
         <is>
           <t>Herbert Spencer González</t>
@@ -1382,7 +1393,7 @@
         </is>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="19" customHeight="1" s="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
           <t>Alfred Thiers Jusan</t>
@@ -1394,7 +1405,7 @@
         </is>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="19" customHeight="1" s="24">
       <c r="A25" s="8" t="inlineStr">
         <is>
           <t>Lorena Herrera Ponce</t>
@@ -1406,7 +1417,7 @@
         </is>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="19" customHeight="1" s="24">
       <c r="A26" s="8" t="inlineStr">
         <is>
           <t>Juan Carlos Jeldes Pontio</t>
@@ -1418,7 +1429,7 @@
         </is>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="19" customHeight="1" s="24">
       <c r="A27" s="8" t="inlineStr">
         <is>
           <t>Michèle Wilkomirsky Uribe</t>
@@ -1430,7 +1441,7 @@
         </is>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="19" customHeight="1" s="24">
       <c r="A28" s="8" t="inlineStr">
         <is>
           <t>Óscar Andrade Castro</t>
@@ -1442,7 +1453,7 @@
         </is>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="19" customHeight="1" s="24">
       <c r="A29" s="8" t="inlineStr">
         <is>
           <t>Anna Braghini</t>
@@ -1454,7 +1465,7 @@
         </is>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="19" customHeight="1" s="24">
       <c r="A30" s="8" t="inlineStr">
         <is>
           <t>Arturo Chicano Jiménez</t>
@@ -1466,7 +1477,7 @@
         </is>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="19" customHeight="1" s="24">
       <c r="A31" s="8" t="inlineStr">
         <is>
           <t>Sylvia Arriagada Cordero</t>
@@ -1478,7 +1489,7 @@
         </is>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="19" customHeight="1" s="24">
       <c r="A32" s="8" t="inlineStr">
         <is>
           <t>Marcelo Araya Aravena</t>
@@ -1490,7 +1501,7 @@
         </is>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="19" customHeight="1" s="24">
       <c r="A33" s="8" t="inlineStr">
         <is>
           <t>Marcelo Araya Aravena</t>
@@ -1502,7 +1513,7 @@
         </is>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="19" customHeight="1" s="24">
       <c r="A34" s="8" t="inlineStr">
         <is>
           <t>Emanuela Di Felice</t>
@@ -1521,10 +1532,10 @@
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="A5:A505" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Nombre no válido" error="El valor debe coincidir con un nombre existente en la hoja correspondiente. Usa el menú desplegable para elegir uno." type="list">
-      <formula1>=InvestigadorNombres</formula1>
+      <formula1>InvestigadorNombres</formula1>
     </dataValidation>
     <dataValidation sqref="B5:B505" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Nombre no válido" error="El valor debe coincidir con un nombre existente en la hoja correspondiente. Usa el menú desplegable para elegir uno." type="list">
-      <formula1>=LabNombres</formula1>
+      <formula1>LabNombres</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1540,25 +1551,23 @@
   <dimension ref="A1:B41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" style="21" min="1" max="1"/>
-    <col width="12" customWidth="1" style="21" min="2" max="2"/>
+    <col width="44.5" customWidth="1" style="24" min="1" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="21">
-      <c r="A1" s="20" t="inlineStr">
+    <row r="1" ht="18" customHeight="1" s="24">
+      <c r="A1" s="25" t="inlineStr">
         <is>
           <t>13 · Investigador ↔ Modo (m:n)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="22" t="inlineStr">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t>Lectura desde el material — modos predominantes declarados o inferidos.</t>
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
@@ -1595,7 +1604,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="30" customHeight="1" s="24">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Katherine Exss Cid</t>
@@ -1619,7 +1628,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="30" customHeight="1" s="24">
       <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Jorge Ferrada Herrera</t>
@@ -1631,7 +1640,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="30" customHeight="1" s="24">
       <c r="A10" s="8" t="inlineStr">
         <is>
           <t>Jorge Ferrada Herrera</t>
@@ -1643,7 +1652,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="30" customHeight="1" s="24">
       <c r="A11" s="8" t="inlineStr">
         <is>
           <t>Andrés Garcés Alzamora</t>
@@ -1655,7 +1664,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="30" customHeight="1" s="24">
       <c r="A12" s="8" t="inlineStr">
         <is>
           <t>Andrés Garcés Alzamora</t>
@@ -1667,7 +1676,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="30" customHeight="1" s="24">
       <c r="A13" s="8" t="inlineStr">
         <is>
           <t>Iván Ivelic Yanes</t>
@@ -1691,7 +1700,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="30" customHeight="1" s="24">
       <c r="A15" s="8" t="inlineStr">
         <is>
           <t>David Luza Cornejo</t>
@@ -1715,7 +1724,7 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="30" customHeight="1" s="24">
       <c r="A17" s="8" t="inlineStr">
         <is>
           <t>Álvaro Mercado Jara</t>
@@ -1751,7 +1760,7 @@
         </is>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="30" customHeight="1" s="24">
       <c r="A20" s="8" t="inlineStr">
         <is>
           <t>Rodrigo Saavedra Venegas</t>
@@ -1763,7 +1772,7 @@
         </is>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="30" customHeight="1" s="24">
       <c r="A21" s="8" t="inlineStr">
         <is>
           <t>Rodrigo Saavedra Venegas</t>
@@ -1775,7 +1784,7 @@
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="30" customHeight="1" s="24">
       <c r="A22" s="8" t="inlineStr">
         <is>
           <t>Daniela Salgado Cofré</t>
@@ -1787,7 +1796,7 @@
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="30" customHeight="1" s="24">
       <c r="A23" s="8" t="inlineStr">
         <is>
           <t>Daniela Salgado Cofré</t>
@@ -1799,7 +1808,7 @@
         </is>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="30" customHeight="1" s="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
           <t>Herbert Spencer González</t>
@@ -1811,7 +1820,7 @@
         </is>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="30" customHeight="1" s="24">
       <c r="A25" s="8" t="inlineStr">
         <is>
           <t>Alfred Thiers Jusan</t>
@@ -1823,7 +1832,7 @@
         </is>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="30" customHeight="1" s="24">
       <c r="A26" s="8" t="inlineStr">
         <is>
           <t>Lorena Herrera Ponce</t>
@@ -1835,7 +1844,7 @@
         </is>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="30" customHeight="1" s="24">
       <c r="A27" s="8" t="inlineStr">
         <is>
           <t>Juan Carlos Jeldes Pontio</t>
@@ -1847,7 +1856,7 @@
         </is>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="30" customHeight="1" s="24">
       <c r="A28" s="8" t="inlineStr">
         <is>
           <t>Michèle Wilkomirsky Uribe</t>
@@ -1859,7 +1868,7 @@
         </is>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="30" customHeight="1" s="24">
       <c r="A29" s="8" t="inlineStr">
         <is>
           <t>Michèle Wilkomirsky Uribe</t>
@@ -1871,7 +1880,7 @@
         </is>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="30" customHeight="1" s="24">
       <c r="A30" s="8" t="inlineStr">
         <is>
           <t>Óscar Andrade Castro</t>
@@ -1883,7 +1892,7 @@
         </is>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="30" customHeight="1" s="24">
       <c r="A31" s="8" t="inlineStr">
         <is>
           <t>Óscar Andrade Castro</t>
@@ -1919,7 +1928,7 @@
         </is>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="30" customHeight="1" s="24">
       <c r="A34" s="8" t="inlineStr">
         <is>
           <t>Arturo Chicano Jiménez</t>
@@ -1931,7 +1940,7 @@
         </is>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="30" customHeight="1" s="24">
       <c r="A35" s="8" t="inlineStr">
         <is>
           <t>Arturo Chicano Jiménez</t>
@@ -1943,7 +1952,7 @@
         </is>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="30" customHeight="1" s="24">
       <c r="A36" s="8" t="inlineStr">
         <is>
           <t>Sylvia Arriagada Cordero</t>
@@ -1955,7 +1964,7 @@
         </is>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="30" customHeight="1" s="24">
       <c r="A37" s="8" t="inlineStr">
         <is>
           <t>Sylvia Arriagada Cordero</t>
@@ -1967,7 +1976,7 @@
         </is>
       </c>
     </row>
-    <row r="38">
+    <row r="38" ht="30" customHeight="1" s="24">
       <c r="A38" s="8" t="inlineStr">
         <is>
           <t>Marcelo Araya Aravena</t>
@@ -1979,7 +1988,7 @@
         </is>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="30" customHeight="1" s="24">
       <c r="A39" s="8" t="inlineStr">
         <is>
           <t>Marcelo Araya Aravena</t>
@@ -1991,7 +2000,7 @@
         </is>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="30" customHeight="1" s="24">
       <c r="A40" s="8" t="inlineStr">
         <is>
           <t>Emanuela Di Felice</t>
@@ -2022,10 +2031,10 @@
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="A5:A505" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Nombre no válido" error="El valor debe coincidir con un nombre existente en la hoja correspondiente. Usa el menú desplegable para elegir uno." type="list">
-      <formula1>=InvestigadorNombres</formula1>
+      <formula1>InvestigadorNombres</formula1>
     </dataValidation>
     <dataValidation sqref="B5:B505" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Nombre no válido" error="El valor debe coincidir con un nombre existente en la hoja correspondiente. Usa el menú desplegable para elegir uno." type="list">
-      <formula1>=ModoNombres</formula1>
+      <formula1>ModoNombres</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2041,25 +2050,25 @@
   <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" style="21" min="1" max="2"/>
-    <col width="18" customWidth="1" style="21" min="3" max="3"/>
+    <col width="35.1640625" customWidth="1" style="24" min="1" max="1"/>
+    <col width="22" customWidth="1" style="24" min="2" max="2"/>
+    <col width="18" customWidth="1" style="24" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="21">
-      <c r="A1" s="20" t="inlineStr">
+    <row r="1" ht="18" customHeight="1" s="24">
+      <c r="A1" s="25" t="inlineStr">
         <is>
           <t>14 · Línea ↔ Modo (m:n)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="22" t="inlineStr">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t>Modos predominantes por Línea — útil para coloreo/filtros del grafo. BORRADOR.</t>
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
@@ -2077,7 +2086,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="60" customHeight="1" s="24">
       <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Personas, interacción y sistemas inclusivos</t>
@@ -2094,7 +2103,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="60" customHeight="1" s="24">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Personas, interacción y sistemas inclusivos</t>
@@ -2111,7 +2120,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="60" customHeight="1" s="24">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Habitar, infraestructura y ecologías territoriales</t>
@@ -2128,7 +2137,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="60" customHeight="1" s="24">
       <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Habitar, infraestructura y ecologías territoriales</t>
@@ -2145,7 +2154,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="60" customHeight="1" s="24">
       <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Teoría e historia de la arquitectura y el diseño</t>
@@ -2162,7 +2171,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="60" customHeight="1" s="24">
       <c r="A10" s="8" t="inlineStr">
         <is>
           <t>Teoría e historia de la arquitectura y el diseño</t>
@@ -2179,7 +2188,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="60" customHeight="1" s="24">
       <c r="A11" s="8" t="inlineStr">
         <is>
           <t>Oficio, tecnologías y aprendizaje proyectual</t>
@@ -2203,10 +2212,10 @@
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="A5:A505" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Nombre no válido" error="El valor debe coincidir con un nombre existente en la hoja correspondiente. Usa el menú desplegable para elegir uno." type="list">
-      <formula1>=LineaNombres</formula1>
+      <formula1>LineaNombres</formula1>
     </dataValidation>
     <dataValidation sqref="B5:B505" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Nombre no válido" error="El valor debe coincidir con un nombre existente en la hoja correspondiente. Usa el menú desplegable para elegir uno." type="list">
-      <formula1>=ModoNombres</formula1>
+      <formula1>ModoNombres</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2222,21 +2231,21 @@
   <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" style="21" min="1" max="1"/>
-    <col width="60" customWidth="1" style="21" min="2" max="2"/>
-    <col width="100" customWidth="1" style="21" min="3" max="3"/>
-    <col width="14" customWidth="1" style="21" min="4" max="4"/>
+    <col width="8" customWidth="1" style="24" min="1" max="1"/>
+    <col width="46.6640625" customWidth="1" style="24" min="2" max="2"/>
+    <col width="100" customWidth="1" style="24" min="3" max="3"/>
+    <col width="14" customWidth="1" style="24" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="21">
-      <c r="A1" s="20" t="inlineStr">
+    <row r="1" ht="18" customHeight="1" s="24">
+      <c r="A1" s="25" t="inlineStr">
         <is>
           <t>15 · Decisiones pendientes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="22" t="inlineStr">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t>Cada decisión bloquea o refina el modelo. Marcar como 'Resuelta' con la respuesta.</t>
         </is>
@@ -2264,7 +2273,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1" s="21">
+    <row r="5" ht="30" customHeight="1" s="24">
       <c r="A5" s="9" t="inlineStr">
         <is>
           <t>D-01</t>
@@ -2286,7 +2295,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1" s="21">
+    <row r="6" ht="30" customHeight="1" s="24">
       <c r="A6" s="9" t="inlineStr">
         <is>
           <t>D-02</t>
@@ -2308,7 +2317,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1" s="21">
+    <row r="7" ht="30" customHeight="1" s="24">
       <c r="A7" s="9" t="inlineStr">
         <is>
           <t>D-03</t>
@@ -2374,7 +2383,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1" s="21">
+    <row r="10" ht="30" customHeight="1" s="24">
       <c r="A10" s="9" t="inlineStr">
         <is>
           <t>D-06</t>
@@ -2396,7 +2405,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1" s="21">
+    <row r="11" ht="30" customHeight="1" s="24">
       <c r="A11" s="9" t="inlineStr">
         <is>
           <t>D-07</t>
@@ -2418,7 +2427,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1" s="21">
+    <row r="12" ht="30" customHeight="1" s="24">
       <c r="A12" s="9" t="inlineStr">
         <is>
           <t>D-08</t>
@@ -2440,7 +2449,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1" s="21">
+    <row r="13" ht="30" customHeight="1" s="24">
       <c r="A13" s="9" t="inlineStr">
         <is>
           <t>D-09</t>
@@ -2462,7 +2471,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1" s="21">
+    <row r="14" ht="30" customHeight="1" s="24">
       <c r="A14" s="9" t="inlineStr">
         <is>
           <t>D-10</t>
@@ -2502,19 +2511,19 @@
   <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" style="21" min="1" max="1"/>
-    <col width="20" customWidth="1" style="21" min="2" max="2"/>
+    <col width="40" customWidth="1" style="24" min="1" max="1"/>
+    <col width="20" customWidth="1" style="24" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="21">
-      <c r="A1" s="20" t="inlineStr">
+    <row r="1" ht="18" customHeight="1" s="24">
+      <c r="A1" s="25" t="inlineStr">
         <is>
           <t>Resumen cuantitativo</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="16" customHeight="1" s="21">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="3" ht="16" customHeight="1" s="24">
+      <c r="A3" s="26" t="inlineStr">
         <is>
           <t>Conteos por entidad (auto-calculados)</t>
         </is>
@@ -2627,7 +2636,7 @@
         </is>
       </c>
       <c r="B13" s="11">
-        <f>COUNTA('09_Sublinea_Tema'!A:A)-1</f>
+        <f>COUNTA('08_Temas'!A:A)-3</f>
         <v/>
       </c>
     </row>
@@ -2708,8 +2717,8 @@
         <v/>
       </c>
     </row>
-    <row r="21" ht="16" customHeight="1" s="21">
-      <c r="A21" s="3" t="inlineStr">
+    <row r="21" ht="16" customHeight="1" s="24">
+      <c r="A21" s="26" t="inlineStr">
         <is>
           <t>Cobertura de mapeos</t>
         </is>
@@ -2722,7 +2731,7 @@
         </is>
       </c>
       <c r="B22">
-        <f>SUMPRODUCT(1/COUNTIF('09_Sublinea_Tema'!B2:B500,'09_Sublinea_Tema'!B2:B500))</f>
+        <f>SUMPRODUCT(('08_Temas'!A5:A500&lt;&gt;"")/COUNTIF('08_Temas'!A5:A500,'08_Temas'!A5:A500&amp;""))</f>
         <v/>
       </c>
     </row>
@@ -2762,20 +2771,20 @@
   <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" style="21" min="1" max="1"/>
-    <col width="38" customWidth="1" style="21" min="2" max="2"/>
-    <col width="110" customWidth="1" style="21" min="3" max="3"/>
+    <col width="10" customWidth="1" style="24" min="1" max="1"/>
+    <col width="38" customWidth="1" style="24" min="2" max="2"/>
+    <col width="110" customWidth="1" style="24" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="21">
-      <c r="A1" s="20" t="inlineStr">
+    <row r="1" ht="18" customHeight="1" s="24">
+      <c r="A1" s="25" t="inlineStr">
         <is>
           <t>17 · Sello formativo del doctorado</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="45" customHeight="1" s="21">
-      <c r="A2" s="23" t="inlineStr">
+    <row r="2" ht="45" customHeight="1" s="24">
+      <c r="A2" s="28" t="inlineStr">
         <is>
           <t>Afirmación identitaria sobre qué se forma. La fila marcada (ELEGIDO, verde) es la versión que se usa para copy institucional. Las otras se conservan como trazabilidad de las alternativas exploradas. Regla de estilo de la elegida: redacción en afirmativo, sin em-dashes.</t>
         </is>
@@ -2798,7 +2807,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="220" customHeight="1" s="21">
+    <row r="5" ht="128" customHeight="1" s="24">
       <c r="A5" s="14" t="n">
         <v>1</v>
       </c>
@@ -2813,7 +2822,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="70" customHeight="1" s="21">
+    <row r="6" ht="35" customHeight="1" s="24">
       <c r="A6" s="15" t="n">
         <v>2</v>
       </c>
@@ -2828,7 +2837,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="70" customHeight="1" s="21">
+    <row r="7" ht="49" customHeight="1" s="24">
       <c r="A7" s="15" t="n">
         <v>3</v>
       </c>
@@ -2843,7 +2852,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="70" customHeight="1" s="21">
+    <row r="8" ht="39" customHeight="1" s="24">
       <c r="A8" s="15" t="n">
         <v>4</v>
       </c>
@@ -2858,7 +2867,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="70" customHeight="1" s="21">
+    <row r="9" ht="33" customHeight="1" s="24">
       <c r="A9" s="15" t="n">
         <v>5</v>
       </c>
@@ -2873,7 +2882,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="70" customHeight="1" s="21">
+    <row r="10" ht="34" customHeight="1" s="24">
       <c r="A10" s="15" t="n">
         <v>6</v>
       </c>
@@ -2906,30 +2915,29 @@
   <dimension ref="A1:E90"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" style="21" min="1" max="1"/>
-    <col width="38" customWidth="1" style="21" min="2" max="2"/>
-    <col width="14" customWidth="1" style="21" min="3" max="3"/>
-    <col width="38" customWidth="1" style="21" min="4" max="4"/>
-    <col width="11" customWidth="1" style="21" min="5" max="5"/>
-    <col width="70" customWidth="1" style="21" min="6" max="6"/>
-    <col width="14" customWidth="1" style="21" min="7" max="7"/>
+    <col width="14" customWidth="1" style="24" min="1" max="1"/>
+    <col width="38" customWidth="1" style="24" min="2" max="2"/>
+    <col width="14" customWidth="1" style="24" min="3" max="3"/>
+    <col width="38" customWidth="1" style="24" min="4" max="4"/>
+    <col width="11" customWidth="1" style="24" min="5" max="5"/>
+    <col width="70" customWidth="1" style="24" min="6" max="6"/>
+    <col width="14" customWidth="1" style="24" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="21">
-      <c r="A1" s="20" t="inlineStr">
+    <row r="1" ht="18" customHeight="1" s="24">
+      <c r="A1" s="25" t="inlineStr">
         <is>
           <t>18 · Proximidad temática (Sublínea ↔ Sublínea)</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="60" customHeight="1" s="21">
-      <c r="A2" s="23" t="inlineStr">
+    <row r="2" ht="60" customHeight="1" s="24">
+      <c r="A2" s="28" t="inlineStr">
         <is>
           <t>Matriz de afinidad declarada como pares simétricos. Inferida desde nombres + descripciones; estado=INFERIDO. Afinar a mano: corregir afinidad, agregar/quitar pares, marcar estado=CONFIRMADO/AJUSTADO/DESCARTADO. Cada par implica afinidad inversa equivalente (b↔a). Si re-generas la planilla con build_xlsx.py, los cambios manuales se sobrescriben — reflejarlos en PROXIMIDAD_PARES del script para que persistan.</t>
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
@@ -2957,7 +2965,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1" s="21">
+    <row r="5" ht="28" customHeight="1" s="24">
       <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Adaptabilidad urbana ante riesgos costeros</t>
@@ -2982,7 +2990,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="28" customHeight="1" s="21">
+    <row r="6" ht="28" customHeight="1" s="24">
       <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Espacios de aprendizaje en contextos vulnerables</t>
@@ -3007,7 +3015,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="42" customHeight="1" s="24">
       <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Accesibilidad cognitiva y codiseño</t>
@@ -3032,7 +3040,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="42" customHeight="1" s="24">
       <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Adaptabilidad urbana ante riesgos costeros</t>
@@ -3057,7 +3065,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="42" customHeight="1" s="24">
       <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Diseño de espacios educativos</t>
@@ -3082,7 +3090,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="42" customHeight="1" s="24">
       <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Diseño de espacios educativos</t>
@@ -3107,7 +3115,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="42" customHeight="1" s="24">
       <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Accesibilidad cognitiva y codiseño</t>
@@ -3132,7 +3140,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="28" customHeight="1" s="21">
+    <row r="12" ht="28" customHeight="1" s="24">
       <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Adaptación formal ante desastres</t>
@@ -3157,7 +3165,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="42" customHeight="1" s="24">
       <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Diseño de espacios educativos</t>
@@ -3182,7 +3190,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="56" customHeight="1" s="24">
       <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Programas educativos y espacios escolares</t>
@@ -3207,7 +3215,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="28" customHeight="1" s="21">
+    <row r="15" ht="28" customHeight="1" s="24">
       <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Saberes técnicos análogos</t>
@@ -3232,7 +3240,7 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="28" customHeight="1" s="24">
       <c r="A16" s="16" t="inlineStr">
         <is>
           <t>Accesibilidad e inclusión</t>
@@ -3257,7 +3265,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="28" customHeight="1" s="21">
+    <row r="17" ht="28" customHeight="1" s="24">
       <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Acervo histórico de Ciudad Abierta y de la Escuela de Arquitectura y Diseño</t>
@@ -3282,7 +3290,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="28" customHeight="1" s="21">
+    <row r="18" ht="28" customHeight="1" s="24">
       <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Arquitectura como medio didáctico</t>
@@ -3307,7 +3315,7 @@
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="42" customHeight="1" s="24">
       <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Arquitectura como medio didáctico</t>
@@ -3332,7 +3340,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="28" customHeight="1" s="21">
+    <row r="20" ht="28" customHeight="1" s="24">
       <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Diseño de espacios educativos</t>
@@ -3357,7 +3365,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="28" customHeight="1" s="21">
+    <row r="21" ht="28" customHeight="1" s="24">
       <c r="A21" s="16" t="inlineStr">
         <is>
           <t>Industrias creativas e innovación social para el desarrollo local</t>
@@ -3382,7 +3390,7 @@
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="28" customHeight="1" s="24">
       <c r="A22" s="16" t="inlineStr">
         <is>
           <t>Perspectivas decoloniales</t>
@@ -3407,7 +3415,7 @@
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="42" customHeight="1" s="24">
       <c r="A23" s="18" t="inlineStr">
         <is>
           <t>Accesibilidad cognitiva y codiseño</t>
@@ -3432,7 +3440,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="28" customHeight="1" s="21">
+    <row r="24" ht="28" customHeight="1" s="24">
       <c r="A24" s="18" t="inlineStr">
         <is>
           <t>Acervo histórico de Ciudad Abierta y de la Escuela de Arquitectura y Diseño</t>
@@ -3457,7 +3465,7 @@
         </is>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="42" customHeight="1" s="24">
       <c r="A25" s="18" t="inlineStr">
         <is>
           <t>Arquitectura como medio didáctico</t>
@@ -3482,7 +3490,7 @@
         </is>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="28" customHeight="1" s="24">
       <c r="A26" s="18" t="inlineStr">
         <is>
           <t>Diseño arquitectónico</t>
@@ -3507,7 +3515,7 @@
         </is>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="28" customHeight="1" s="24">
       <c r="A27" s="18" t="inlineStr">
         <is>
           <t>El vacío arquitectónico</t>
@@ -3532,7 +3540,7 @@
         </is>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="28" customHeight="1" s="24">
       <c r="A28" s="18" t="inlineStr">
         <is>
           <t>Perspectivas decoloniales</t>
@@ -3557,7 +3565,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="28" customHeight="1" s="21">
+    <row r="29" ht="28" customHeight="1" s="24">
       <c r="A29" s="18" t="inlineStr">
         <is>
           <t>Accesibilidad cognitiva y codiseño</t>
@@ -3582,7 +3590,7 @@
         </is>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="28" customHeight="1" s="24">
       <c r="A30" s="18" t="inlineStr">
         <is>
           <t>Accesibilidad e inclusión</t>
@@ -3607,7 +3615,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="28" customHeight="1" s="21">
+    <row r="31" ht="28" customHeight="1" s="24">
       <c r="A31" s="18" t="inlineStr">
         <is>
           <t>Acervo histórico de Ciudad Abierta y de la Escuela de Arquitectura y Diseño</t>
@@ -3632,7 +3640,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="28" customHeight="1" s="21">
+    <row r="32" ht="28" customHeight="1" s="24">
       <c r="A32" s="18" t="inlineStr">
         <is>
           <t>Acervo histórico de Ciudad Abierta y de la Escuela de Arquitectura y Diseño</t>
@@ -3657,7 +3665,7 @@
         </is>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="42" customHeight="1" s="24">
       <c r="A33" s="18" t="inlineStr">
         <is>
           <t>Comunicación aumentativa y alternativa</t>
@@ -3682,7 +3690,7 @@
         </is>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="28" customHeight="1" s="24">
       <c r="A34" s="18" t="inlineStr">
         <is>
           <t>Diseño arquitectónico</t>
@@ -3707,7 +3715,7 @@
         </is>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="28" customHeight="1" s="24">
       <c r="A35" s="18" t="inlineStr">
         <is>
           <t>Diseño arquitectónico</t>
@@ -3732,7 +3740,7 @@
         </is>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="42" customHeight="1" s="24">
       <c r="A36" s="18" t="inlineStr">
         <is>
           <t>Diseño de espacios educativos</t>
@@ -3757,7 +3765,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="28" customHeight="1" s="21">
+    <row r="37" ht="28" customHeight="1" s="24">
       <c r="A37" s="18" t="inlineStr">
         <is>
           <t>Espacios de aprendizaje en contextos vulnerables</t>
@@ -3782,7 +3790,7 @@
         </is>
       </c>
     </row>
-    <row r="38">
+    <row r="38" ht="42" customHeight="1" s="24">
       <c r="A38" s="18" t="inlineStr">
         <is>
           <t>Espacios de estimulación temprana</t>
@@ -3807,7 +3815,7 @@
         </is>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="56" customHeight="1" s="24">
       <c r="A39" s="18" t="inlineStr">
         <is>
           <t>Espacios educativos en contextos vulnerables</t>
@@ -3832,7 +3840,7 @@
         </is>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="42" customHeight="1" s="24">
       <c r="A40" s="18" t="inlineStr">
         <is>
           <t>Formación en pensamiento y acción creativa</t>
@@ -3857,7 +3865,7 @@
         </is>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="28" customHeight="1" s="24">
       <c r="A41" s="18" t="inlineStr">
         <is>
           <t>Perspectivas decoloniales</t>
@@ -3882,7 +3890,7 @@
         </is>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="28" customHeight="1" s="24">
       <c r="A42" s="18" t="inlineStr">
         <is>
           <t>Prácticas colectivas</t>
@@ -3907,7 +3915,7 @@
         </is>
       </c>
     </row>
-    <row r="43">
+    <row r="43" ht="28" customHeight="1" s="24">
       <c r="A43" s="18" t="inlineStr">
         <is>
           <t>El sentido de la hospitalidad</t>
@@ -3932,7 +3940,7 @@
         </is>
       </c>
     </row>
-    <row r="44">
+    <row r="44" ht="42" customHeight="1" s="24">
       <c r="A44" s="18" t="inlineStr">
         <is>
           <t>Accesibilidad cognitiva y codiseño</t>
@@ -3957,7 +3965,7 @@
         </is>
       </c>
     </row>
-    <row r="45">
+    <row r="45" ht="42" customHeight="1" s="24">
       <c r="A45" s="18" t="inlineStr">
         <is>
           <t>Accesibilidad cognitiva y codiseño</t>
@@ -3982,7 +3990,7 @@
         </is>
       </c>
     </row>
-    <row r="46">
+    <row r="46" ht="28" customHeight="1" s="24">
       <c r="A46" s="18" t="inlineStr">
         <is>
           <t>Accesibilidad e inclusión</t>
@@ -4007,7 +4015,7 @@
         </is>
       </c>
     </row>
-    <row r="47">
+    <row r="47" ht="42" customHeight="1" s="24">
       <c r="A47" s="18" t="inlineStr">
         <is>
           <t>Adaptabilidad urbana ante riesgos costeros</t>
@@ -4032,7 +4040,7 @@
         </is>
       </c>
     </row>
-    <row r="48">
+    <row r="48" ht="42" customHeight="1" s="24">
       <c r="A48" s="18" t="inlineStr">
         <is>
           <t>Arquitectura como medio didáctico</t>
@@ -4057,7 +4065,7 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="28" customHeight="1" s="21">
+    <row r="49" ht="28" customHeight="1" s="24">
       <c r="A49" s="18" t="inlineStr">
         <is>
           <t>Comunicación aumentativa y alternativa</t>
@@ -4082,7 +4090,7 @@
         </is>
       </c>
     </row>
-    <row r="50">
+    <row r="50" ht="28" customHeight="1" s="24">
       <c r="A50" s="18" t="inlineStr">
         <is>
           <t>Diseño arquitectónico</t>
@@ -4107,7 +4115,7 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="28" customHeight="1" s="21">
+    <row r="51" ht="28" customHeight="1" s="24">
       <c r="A51" s="18" t="inlineStr">
         <is>
           <t>Diseño de espacios educativos</t>
@@ -4132,7 +4140,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="28" customHeight="1" s="21">
+    <row r="52" ht="28" customHeight="1" s="24">
       <c r="A52" s="18" t="inlineStr">
         <is>
           <t>Diseño de interacción, servicios y experiencia de usuario</t>
@@ -4157,7 +4165,7 @@
         </is>
       </c>
     </row>
-    <row r="53">
+    <row r="53" ht="28" customHeight="1" s="24">
       <c r="A53" s="18" t="inlineStr">
         <is>
           <t>El vacío arquitectónico</t>
@@ -4182,7 +4190,7 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="28" customHeight="1" s="21">
+    <row r="54" ht="28" customHeight="1" s="24">
       <c r="A54" s="18" t="inlineStr">
         <is>
           <t>Espacios de aprendizaje en contextos vulnerables</t>
@@ -4207,7 +4215,7 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="28" customHeight="1" s="21">
+    <row r="55" ht="28" customHeight="1" s="24">
       <c r="A55" s="18" t="inlineStr">
         <is>
           <t>Industrias creativas e innovación social para el desarrollo local</t>
@@ -4232,7 +4240,7 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="28" customHeight="1" s="21">
+    <row r="56" ht="28" customHeight="1" s="24">
       <c r="A56" s="18" t="inlineStr">
         <is>
           <t>Medios de aprendizaje en arquitectura y diseño</t>
@@ -4257,7 +4265,7 @@
         </is>
       </c>
     </row>
-    <row r="57">
+    <row r="57" ht="28" customHeight="1" s="24">
       <c r="A57" s="18" t="inlineStr">
         <is>
           <t>Métodos de diseño</t>
@@ -4282,7 +4290,7 @@
         </is>
       </c>
     </row>
-    <row r="58">
+    <row r="58" ht="28" customHeight="1" s="24">
       <c r="A58" s="18" t="inlineStr">
         <is>
           <t>Prácticas colectivas</t>
@@ -4307,7 +4315,7 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="28" customHeight="1" s="21">
+    <row r="59" ht="28" customHeight="1" s="24">
       <c r="A59" s="18" t="inlineStr">
         <is>
           <t>Urbanización, urbanismo y ecología política</t>
@@ -4332,7 +4340,7 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="28" customHeight="1" s="21">
+    <row r="60" ht="28" customHeight="1" s="24">
       <c r="A60" s="18" t="inlineStr">
         <is>
           <t>Accesibilidad e inclusión</t>
@@ -4357,7 +4365,7 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="28" customHeight="1" s="21">
+    <row r="61" ht="28" customHeight="1" s="24">
       <c r="A61" s="18" t="inlineStr">
         <is>
           <t>Accesibilidad e inclusión</t>
@@ -4382,7 +4390,7 @@
         </is>
       </c>
     </row>
-    <row r="62">
+    <row r="62" ht="28" customHeight="1" s="24">
       <c r="A62" s="18" t="inlineStr">
         <is>
           <t>Accesibilidad e inclusión</t>
@@ -4407,7 +4415,7 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="28" customHeight="1" s="21">
+    <row r="63" ht="28" customHeight="1" s="24">
       <c r="A63" s="18" t="inlineStr">
         <is>
           <t>Acervo histórico de Ciudad Abierta y de la Escuela de Arquitectura y Diseño</t>
@@ -4432,7 +4440,7 @@
         </is>
       </c>
     </row>
-    <row r="64">
+    <row r="64" ht="42" customHeight="1" s="24">
       <c r="A64" s="18" t="inlineStr">
         <is>
           <t>Adaptación formal ante desastres</t>
@@ -4457,7 +4465,7 @@
         </is>
       </c>
     </row>
-    <row r="65">
+    <row r="65" ht="42" customHeight="1" s="24">
       <c r="A65" s="18" t="inlineStr">
         <is>
           <t>Adaptación formal ante desastres</t>
@@ -4482,7 +4490,7 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="28" customHeight="1" s="21">
+    <row r="66" ht="28" customHeight="1" s="24">
       <c r="A66" s="18" t="inlineStr">
         <is>
           <t>Arquitectura como medio didáctico</t>
@@ -4507,7 +4515,7 @@
         </is>
       </c>
     </row>
-    <row r="67">
+    <row r="67" ht="28" customHeight="1" s="24">
       <c r="A67" s="18" t="inlineStr">
         <is>
           <t>Diseño arquitectónico</t>
@@ -4532,7 +4540,7 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="28" customHeight="1" s="21">
+    <row r="68" ht="28" customHeight="1" s="24">
       <c r="A68" s="18" t="inlineStr">
         <is>
           <t>Diseño de interacción, servicios y experiencia de usuario</t>
@@ -4557,7 +4565,7 @@
         </is>
       </c>
     </row>
-    <row r="69">
+    <row r="69" ht="28" customHeight="1" s="24">
       <c r="A69" s="18" t="inlineStr">
         <is>
           <t>El sentido de la hospitalidad</t>
@@ -4582,7 +4590,7 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="28" customHeight="1" s="21">
+    <row r="70" ht="28" customHeight="1" s="24">
       <c r="A70" s="18" t="inlineStr">
         <is>
           <t>Formación en pensamiento y acción creativa</t>
@@ -4607,7 +4615,7 @@
         </is>
       </c>
     </row>
-    <row r="71">
+    <row r="71" ht="42" customHeight="1" s="24">
       <c r="A71" s="18" t="inlineStr">
         <is>
           <t>Formación en pensamiento y acción creativa</t>
@@ -4632,7 +4640,7 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="28" customHeight="1" s="21">
+    <row r="72" ht="28" customHeight="1" s="24">
       <c r="A72" s="18" t="inlineStr">
         <is>
           <t>Industrias creativas e innovación social para el desarrollo local</t>
@@ -4657,7 +4665,7 @@
         </is>
       </c>
     </row>
-    <row r="73">
+    <row r="73" ht="42" customHeight="1" s="24">
       <c r="A73" s="18" t="inlineStr">
         <is>
           <t>Teoría e historia de la arquitectura</t>
@@ -4682,7 +4690,7 @@
         </is>
       </c>
     </row>
-    <row r="74">
+    <row r="74" ht="28" customHeight="1" s="24">
       <c r="A74" s="18" t="inlineStr">
         <is>
           <t>Accesibilidad e inclusión</t>
@@ -4707,7 +4715,7 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="28" customHeight="1" s="21">
+    <row r="75" ht="28" customHeight="1" s="24">
       <c r="A75" s="18" t="inlineStr">
         <is>
           <t>Acervo histórico de Ciudad Abierta y de la Escuela de Arquitectura y Diseño</t>
@@ -4732,7 +4740,7 @@
         </is>
       </c>
     </row>
-    <row r="76">
+    <row r="76" ht="42" customHeight="1" s="24">
       <c r="A76" s="18" t="inlineStr">
         <is>
           <t>Arquitectura como medio didáctico</t>
@@ -4757,7 +4765,7 @@
         </is>
       </c>
     </row>
-    <row r="77">
+    <row r="77" ht="42" customHeight="1" s="24">
       <c r="A77" s="18" t="inlineStr">
         <is>
           <t>Arquitectura como medio didáctico</t>
@@ -4782,7 +4790,7 @@
         </is>
       </c>
     </row>
-    <row r="78">
+    <row r="78" ht="28" customHeight="1" s="24">
       <c r="A78" s="18" t="inlineStr">
         <is>
           <t>Diseño y vida independiente</t>
@@ -4807,7 +4815,7 @@
         </is>
       </c>
     </row>
-    <row r="79">
+    <row r="79" ht="28" customHeight="1" s="24">
       <c r="A79" s="18" t="inlineStr">
         <is>
           <t>El sentido de la hospitalidad</t>
@@ -4832,7 +4840,7 @@
         </is>
       </c>
     </row>
-    <row r="80" ht="28" customHeight="1" s="21">
+    <row r="80" ht="28" customHeight="1" s="24">
       <c r="A80" s="18" t="inlineStr">
         <is>
           <t>Formación en pensamiento y acción creativa</t>
@@ -4857,7 +4865,7 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="28" customHeight="1" s="21">
+    <row r="81" ht="28" customHeight="1" s="24">
       <c r="A81" s="18" t="inlineStr">
         <is>
           <t>Industrias creativas e innovación social para el desarrollo local</t>
@@ -4882,7 +4890,7 @@
         </is>
       </c>
     </row>
-    <row r="82">
+    <row r="82" ht="42" customHeight="1" s="24">
       <c r="A82" s="18" t="inlineStr">
         <is>
           <t>Accesibilidad cognitiva y codiseño</t>
@@ -4907,7 +4915,7 @@
         </is>
       </c>
     </row>
-    <row r="83" ht="28" customHeight="1" s="21">
+    <row r="83" ht="28" customHeight="1" s="24">
       <c r="A83" s="18" t="inlineStr">
         <is>
           <t>Acervo histórico de Ciudad Abierta y de la Escuela de Arquitectura y Diseño</t>
@@ -4932,7 +4940,7 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="28" customHeight="1" s="21">
+    <row r="84" ht="28" customHeight="1" s="24">
       <c r="A84" s="18" t="inlineStr">
         <is>
           <t>Acervo histórico de Ciudad Abierta y de la Escuela de Arquitectura y Diseño</t>
@@ -4957,7 +4965,7 @@
         </is>
       </c>
     </row>
-    <row r="85" ht="28" customHeight="1" s="21">
+    <row r="85" ht="28" customHeight="1" s="24">
       <c r="A85" s="18" t="inlineStr">
         <is>
           <t>Diseño arquitectónico</t>
@@ -4982,7 +4990,7 @@
         </is>
       </c>
     </row>
-    <row r="86" ht="28" customHeight="1" s="21">
+    <row r="86" ht="28" customHeight="1" s="24">
       <c r="A86" s="18" t="inlineStr">
         <is>
           <t>Diseño y vida independiente</t>
@@ -5007,7 +5015,7 @@
         </is>
       </c>
     </row>
-    <row r="87" ht="28" customHeight="1" s="21">
+    <row r="87" ht="28" customHeight="1" s="24">
       <c r="A87" s="18" t="inlineStr">
         <is>
           <t>Formación en pensamiento y acción creativa</t>
@@ -5032,7 +5040,7 @@
         </is>
       </c>
     </row>
-    <row r="88" ht="28" customHeight="1" s="21">
+    <row r="88" ht="28" customHeight="1" s="24">
       <c r="A88" s="18" t="inlineStr">
         <is>
           <t>Industrias creativas e innovación social para el desarrollo local</t>
@@ -5057,7 +5065,7 @@
         </is>
       </c>
     </row>
-    <row r="89" ht="28" customHeight="1" s="21">
+    <row r="89" ht="28" customHeight="1" s="24">
       <c r="A89" s="18" t="inlineStr">
         <is>
           <t>Métodos de diseño</t>
@@ -5082,7 +5090,7 @@
         </is>
       </c>
     </row>
-    <row r="90">
+    <row r="90" ht="42" customHeight="1" s="24">
       <c r="A90" s="18" t="inlineStr">
         <is>
           <t>Proyecto de arquitectura escolar</t>
@@ -5113,15 +5121,12 @@
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="2">
     <dataValidation sqref="G5:G90" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"INFERIDO,CONFIRMADO,AJUSTADO,DESCARTADO"</formula1>
     </dataValidation>
-    <dataValidation sqref="A5:A505" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Nombre no válido" error="El valor debe coincidir con un nombre existente en la hoja correspondiente. Usa el menú desplegable para elegir uno." type="list">
-      <formula1>=SublineaNombres</formula1>
-    </dataValidation>
-    <dataValidation sqref="B5:B505" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Nombre no válido" error="El valor debe coincidir con un nombre existente en la hoja correspondiente. Usa el menú desplegable para elegir uno." type="list">
-      <formula1>=SublineaNombres</formula1>
+    <dataValidation sqref="A5:B505" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Nombre no válido" error="El valor debe coincidir con un nombre existente en la hoja correspondiente. Usa el menú desplegable para elegir uno." type="list">
+      <formula1>SublineaNombres</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5137,27 +5142,26 @@
   <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" style="21" min="1" max="1"/>
-    <col width="55" customWidth="1" style="21" min="2" max="2"/>
-    <col width="95" customWidth="1" style="21" min="3" max="3"/>
-    <col width="26" customWidth="1" style="21" min="4" max="4"/>
+    <col width="12" customWidth="1" style="24" min="1" max="1"/>
+    <col width="55" customWidth="1" style="24" min="2" max="2"/>
+    <col width="95" customWidth="1" style="24" min="3" max="3"/>
+    <col width="26" customWidth="1" style="24" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="21">
-      <c r="A1" s="20" t="inlineStr">
+    <row r="1" ht="18" customHeight="1" s="24">
+      <c r="A1" s="25" t="inlineStr">
         <is>
           <t>01 · Líneas troncales (4 a definir — BORRADOR)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="22" t="inlineStr">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t>Cada Sublínea pertenece a una Línea. Los Laboratorios pueden sostener una o varias Líneas. Borrador derivado de la hipótesis de compactación.</t>
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
@@ -5180,7 +5184,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="45" customHeight="1" s="21">
+    <row r="5" ht="45" customHeight="1" s="24">
       <c r="A5" s="8" t="inlineStr">
         <is>
           <t>LIN-01</t>
@@ -5202,7 +5206,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="45" customHeight="1" s="21">
+    <row r="6" ht="45" customHeight="1" s="24">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>LIN-02</t>
@@ -5224,7 +5228,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="45" customHeight="1" s="21">
+    <row r="7" ht="45" customHeight="1" s="24">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>LIN-03</t>
@@ -5246,7 +5250,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1" s="21">
+    <row r="8" ht="30" customHeight="1" s="24">
       <c r="A8" s="8" t="inlineStr">
         <is>
           <t>LIN-04</t>
@@ -5286,28 +5290,27 @@
   <dimension ref="A1:E57"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" style="21" min="1" max="1"/>
-    <col width="55" customWidth="1" style="21" min="2" max="2"/>
-    <col width="12" customWidth="1" style="21" min="3" max="3"/>
-    <col width="10" customWidth="1" style="21" min="4" max="4"/>
-    <col width="50" customWidth="1" style="21" min="5" max="5"/>
+    <col width="10" customWidth="1" style="24" min="1" max="1"/>
+    <col width="55" customWidth="1" style="24" min="2" max="2"/>
+    <col width="21.33203125" customWidth="1" style="24" min="3" max="3"/>
+    <col width="23.33203125" customWidth="1" style="24" min="4" max="4"/>
+    <col width="50" customWidth="1" style="24" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="21">
-      <c r="A1" s="20" t="inlineStr">
+    <row r="1" ht="18" customHeight="1" s="24">
+      <c r="A1" s="25" t="inlineStr">
         <is>
           <t>02 · Sublíneas (banco depurado, ~30)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="22" t="inlineStr">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t>Cada sublínea pertenece a UNA línea troncal. La asignación linea_id es BORRADOR — revisar caso por caso.</t>
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
@@ -5335,7 +5338,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="60" customHeight="1" s="24">
       <c r="A5" s="8" t="inlineStr">
         <is>
           <t>SUB-01</t>
@@ -5358,7 +5361,7 @@
       </c>
       <c r="E5" s="8" t="n"/>
     </row>
-    <row r="6">
+    <row r="6" ht="60" customHeight="1" s="24">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>SUB-02</t>
@@ -5381,7 +5384,7 @@
       </c>
       <c r="E6" s="8" t="n"/>
     </row>
-    <row r="7" ht="30" customHeight="1" s="21">
+    <row r="7" ht="30" customHeight="1" s="24">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>SUB-03</t>
@@ -5404,7 +5407,7 @@
       </c>
       <c r="E7" s="8" t="n"/>
     </row>
-    <row r="8">
+    <row r="8" ht="60" customHeight="1" s="24">
       <c r="A8" s="8" t="inlineStr">
         <is>
           <t>SUB-04</t>
@@ -5427,7 +5430,7 @@
       </c>
       <c r="E8" s="8" t="n"/>
     </row>
-    <row r="9">
+    <row r="9" ht="60" customHeight="1" s="24">
       <c r="A9" s="8" t="inlineStr">
         <is>
           <t>SUB-05</t>
@@ -5450,7 +5453,7 @@
       </c>
       <c r="E9" s="8" t="n"/>
     </row>
-    <row r="10">
+    <row r="10" ht="75" customHeight="1" s="24">
       <c r="A10" s="8" t="inlineStr">
         <is>
           <t>SUB-06</t>
@@ -5477,7 +5480,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="60" customHeight="1" s="24">
       <c r="A11" s="8" t="inlineStr">
         <is>
           <t>SUB-07</t>
@@ -5500,7 +5503,7 @@
       </c>
       <c r="E11" s="8" t="n"/>
     </row>
-    <row r="12">
+    <row r="12" ht="75" customHeight="1" s="24">
       <c r="A12" s="8" t="inlineStr">
         <is>
           <t>SUB-08</t>
@@ -5523,7 +5526,7 @@
       </c>
       <c r="E12" s="8" t="n"/>
     </row>
-    <row r="13">
+    <row r="13" ht="75" customHeight="1" s="24">
       <c r="A13" s="8" t="inlineStr">
         <is>
           <t>SUB-09</t>
@@ -5550,7 +5553,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="60" customHeight="1" s="24">
       <c r="A14" s="8" t="inlineStr">
         <is>
           <t>SUB-10</t>
@@ -5573,7 +5576,7 @@
       </c>
       <c r="E14" s="8" t="n"/>
     </row>
-    <row r="15">
+    <row r="15" ht="60" customHeight="1" s="24">
       <c r="A15" s="8" t="inlineStr">
         <is>
           <t>SUB-11</t>
@@ -5596,7 +5599,7 @@
       </c>
       <c r="E15" s="8" t="n"/>
     </row>
-    <row r="16">
+    <row r="16" ht="75" customHeight="1" s="24">
       <c r="A16" s="8" t="inlineStr">
         <is>
           <t>SUB-12</t>
@@ -5619,7 +5622,7 @@
       </c>
       <c r="E16" s="8" t="n"/>
     </row>
-    <row r="17">
+    <row r="17" ht="75" customHeight="1" s="24">
       <c r="A17" s="8" t="inlineStr">
         <is>
           <t>SUB-13</t>
@@ -5642,7 +5645,7 @@
       </c>
       <c r="E17" s="8" t="n"/>
     </row>
-    <row r="18">
+    <row r="18" ht="75" customHeight="1" s="24">
       <c r="A18" s="8" t="inlineStr">
         <is>
           <t>SUB-14</t>
@@ -5669,7 +5672,7 @@
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="75" customHeight="1" s="24">
       <c r="A19" s="8" t="inlineStr">
         <is>
           <t>SUB-15</t>
@@ -5696,7 +5699,7 @@
         </is>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="75" customHeight="1" s="24">
       <c r="A20" s="8" t="inlineStr">
         <is>
           <t>SUB-16</t>
@@ -5723,7 +5726,7 @@
         </is>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="60" customHeight="1" s="24">
       <c r="A21" s="8" t="inlineStr">
         <is>
           <t>SUB-17</t>
@@ -5746,7 +5749,7 @@
       </c>
       <c r="E21" s="8" t="n"/>
     </row>
-    <row r="22">
+    <row r="22" ht="60" customHeight="1" s="24">
       <c r="A22" s="8" t="inlineStr">
         <is>
           <t>SUB-18</t>
@@ -5769,7 +5772,7 @@
       </c>
       <c r="E22" s="8" t="n"/>
     </row>
-    <row r="23">
+    <row r="23" ht="75" customHeight="1" s="24">
       <c r="A23" s="8" t="inlineStr">
         <is>
           <t>SUB-19</t>
@@ -5796,7 +5799,7 @@
         </is>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="60" customHeight="1" s="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
           <t>SUB-20</t>
@@ -5819,7 +5822,7 @@
       </c>
       <c r="E24" s="8" t="n"/>
     </row>
-    <row r="25">
+    <row r="25" ht="60" customHeight="1" s="24">
       <c r="A25" s="8" t="inlineStr">
         <is>
           <t>SUB-21</t>
@@ -5846,7 +5849,7 @@
         </is>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="75" customHeight="1" s="24">
       <c r="A26" s="8" t="inlineStr">
         <is>
           <t>SUB-22</t>
@@ -5873,7 +5876,7 @@
         </is>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="75" customHeight="1" s="24">
       <c r="A27" s="8" t="inlineStr">
         <is>
           <t>SUB-23</t>
@@ -5900,7 +5903,7 @@
         </is>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="75" customHeight="1" s="24">
       <c r="A28" s="8" t="inlineStr">
         <is>
           <t>SUB-24</t>
@@ -5927,7 +5930,7 @@
         </is>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="60" customHeight="1" s="24">
       <c r="A29" s="8" t="inlineStr">
         <is>
           <t>SUB-25</t>
@@ -5950,7 +5953,7 @@
       </c>
       <c r="E29" s="8" t="n"/>
     </row>
-    <row r="30">
+    <row r="30" ht="75" customHeight="1" s="24">
       <c r="A30" s="8" t="inlineStr">
         <is>
           <t>SUB-26</t>
@@ -5973,7 +5976,7 @@
       </c>
       <c r="E30" s="8" t="n"/>
     </row>
-    <row r="31" ht="30" customHeight="1" s="21">
+    <row r="31" ht="30" customHeight="1" s="24">
       <c r="A31" s="8" t="inlineStr">
         <is>
           <t>SUB-27</t>
@@ -5996,7 +5999,7 @@
       </c>
       <c r="E31" s="8" t="n"/>
     </row>
-    <row r="32">
+    <row r="32" ht="60" customHeight="1" s="24">
       <c r="A32" s="8" t="inlineStr">
         <is>
           <t>SUB-28</t>
@@ -6019,7 +6022,7 @@
       </c>
       <c r="E32" s="8" t="n"/>
     </row>
-    <row r="33">
+    <row r="33" ht="60" customHeight="1" s="24">
       <c r="A33" s="8" t="inlineStr">
         <is>
           <t>SUB-29</t>
@@ -6042,7 +6045,7 @@
       </c>
       <c r="E33" s="8" t="n"/>
     </row>
-    <row r="34">
+    <row r="34" ht="60" customHeight="1" s="24">
       <c r="A34" s="8" t="inlineStr">
         <is>
           <t>SUB-30</t>
@@ -6065,7 +6068,7 @@
       </c>
       <c r="E34" s="8" t="n"/>
     </row>
-    <row r="35">
+    <row r="35" ht="60" customHeight="1" s="24">
       <c r="A35" s="8" t="inlineStr">
         <is>
           <t>SUB-31</t>
@@ -6092,7 +6095,7 @@
         </is>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="60" customHeight="1" s="24">
       <c r="A36" s="8" t="inlineStr">
         <is>
           <t>SUB-32</t>
@@ -6119,7 +6122,7 @@
         </is>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="60" customHeight="1" s="24">
       <c r="A37" s="8" t="inlineStr">
         <is>
           <t>SUB-33</t>
@@ -6146,7 +6149,7 @@
         </is>
       </c>
     </row>
-    <row r="38">
+    <row r="38" ht="60" customHeight="1" s="24">
       <c r="A38" s="8" t="inlineStr">
         <is>
           <t>SUB-34</t>
@@ -6173,7 +6176,7 @@
         </is>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="60" customHeight="1" s="24">
       <c r="A39" s="8" t="inlineStr">
         <is>
           <t>SUB-35</t>
@@ -6200,7 +6203,7 @@
         </is>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="60" customHeight="1" s="24">
       <c r="A40" s="8" t="inlineStr">
         <is>
           <t>SUB-36</t>
@@ -6227,7 +6230,7 @@
         </is>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="60" customHeight="1" s="24">
       <c r="A41" s="8" t="inlineStr">
         <is>
           <t>SUB-37</t>
@@ -6254,7 +6257,7 @@
         </is>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="60" customHeight="1" s="24">
       <c r="A42" s="8" t="inlineStr">
         <is>
           <t>SUB-38</t>
@@ -6281,7 +6284,7 @@
         </is>
       </c>
     </row>
-    <row r="43">
+    <row r="43" ht="60" customHeight="1" s="24">
       <c r="A43" s="8" t="inlineStr">
         <is>
           <t>SUB-39</t>
@@ -6308,7 +6311,7 @@
         </is>
       </c>
     </row>
-    <row r="44">
+    <row r="44" ht="60" customHeight="1" s="24">
       <c r="A44" s="8" t="inlineStr">
         <is>
           <t>SUB-40</t>
@@ -6335,7 +6338,7 @@
         </is>
       </c>
     </row>
-    <row r="45">
+    <row r="45" ht="60" customHeight="1" s="24">
       <c r="A45" s="8" t="inlineStr">
         <is>
           <t>SUB-41</t>
@@ -6362,7 +6365,7 @@
         </is>
       </c>
     </row>
-    <row r="46">
+    <row r="46" ht="60" customHeight="1" s="24">
       <c r="A46" s="8" t="inlineStr">
         <is>
           <t>SUB-42</t>
@@ -6389,7 +6392,7 @@
         </is>
       </c>
     </row>
-    <row r="47">
+    <row r="47" ht="60" customHeight="1" s="24">
       <c r="A47" s="8" t="inlineStr">
         <is>
           <t>SUB-43</t>
@@ -6416,7 +6419,7 @@
         </is>
       </c>
     </row>
-    <row r="48">
+    <row r="48" ht="60" customHeight="1" s="24">
       <c r="A48" s="8" t="inlineStr">
         <is>
           <t>SUB-44</t>
@@ -6443,7 +6446,7 @@
         </is>
       </c>
     </row>
-    <row r="49">
+    <row r="49" ht="60" customHeight="1" s="24">
       <c r="A49" s="8" t="inlineStr">
         <is>
           <t>SUB-45</t>
@@ -6470,7 +6473,7 @@
         </is>
       </c>
     </row>
-    <row r="50">
+    <row r="50" ht="60" customHeight="1" s="24">
       <c r="A50" s="8" t="inlineStr">
         <is>
           <t>SUB-46</t>
@@ -6497,7 +6500,7 @@
         </is>
       </c>
     </row>
-    <row r="51">
+    <row r="51" ht="60" customHeight="1" s="24">
       <c r="A51" s="8" t="inlineStr">
         <is>
           <t>SUB-47</t>
@@ -6524,7 +6527,7 @@
         </is>
       </c>
     </row>
-    <row r="52">
+    <row r="52" ht="75" customHeight="1" s="24">
       <c r="A52" s="8" t="inlineStr">
         <is>
           <t>SUB-48</t>
@@ -6551,7 +6554,7 @@
         </is>
       </c>
     </row>
-    <row r="53">
+    <row r="53" ht="75" customHeight="1" s="24">
       <c r="A53" s="8" t="inlineStr">
         <is>
           <t>SUB-49</t>
@@ -6578,7 +6581,7 @@
         </is>
       </c>
     </row>
-    <row r="54">
+    <row r="54" ht="75" customHeight="1" s="24">
       <c r="A54" s="8" t="inlineStr">
         <is>
           <t>SUB-50</t>
@@ -6605,7 +6608,7 @@
         </is>
       </c>
     </row>
-    <row r="55">
+    <row r="55" ht="75" customHeight="1" s="24">
       <c r="A55" s="8" t="inlineStr">
         <is>
           <t>SUB-51</t>
@@ -6632,7 +6635,7 @@
         </is>
       </c>
     </row>
-    <row r="56">
+    <row r="56" ht="75" customHeight="1" s="24">
       <c r="A56" s="8" t="inlineStr">
         <is>
           <t>SUB-52</t>
@@ -6659,7 +6662,7 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="30" customHeight="1" s="21">
+    <row r="57" ht="30" customHeight="1" s="24">
       <c r="A57" s="8" t="inlineStr">
         <is>
           <t>SUB-53</t>
@@ -6693,10 +6696,10 @@
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="C5:C505" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Nombre no válido" error="El valor debe coincidir con un nombre existente en la hoja correspondiente. Usa el menú desplegable para elegir uno." type="list">
-      <formula1>=LineaNombres</formula1>
+      <formula1>LineaNombres</formula1>
     </dataValidation>
     <dataValidation sqref="D5:D505" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Nombre no válido" error="El valor debe coincidir con un nombre existente en la hoja correspondiente. Usa el menú desplegable para elegir uno." type="list">
-      <formula1>=AreaNombres</formula1>
+      <formula1>AreaNombres</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6712,26 +6715,25 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" style="21" min="1" max="1"/>
-    <col width="50" customWidth="1" style="21" min="2" max="2"/>
-    <col width="110" customWidth="1" style="21" min="3" max="3"/>
+    <col width="10" customWidth="1" style="24" min="1" max="1"/>
+    <col width="50" customWidth="1" style="24" min="2" max="2"/>
+    <col width="110" customWidth="1" style="24" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="21">
-      <c r="A1" s="20" t="inlineStr">
+    <row r="1" ht="18" customHeight="1" s="24">
+      <c r="A1" s="25" t="inlineStr">
         <is>
           <t>03 · Áreas del Postgrado</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="22" t="inlineStr">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t>Eje ortogonal a las Líneas. Marcos amplios, no compartimentos.</t>
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
@@ -6749,7 +6751,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1" s="21">
+    <row r="5" ht="30" customHeight="1" s="24">
       <c r="A5" s="8" t="inlineStr">
         <is>
           <t>ECH</t>
@@ -6766,7 +6768,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1" s="21">
+    <row r="6" ht="30" customHeight="1" s="24">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>EAA</t>
@@ -6783,7 +6785,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1" s="21">
+    <row r="7" ht="30" customHeight="1" s="24">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>FCT</t>
@@ -6818,13 +6820,13 @@
   <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" style="21" min="1" max="1"/>
-    <col width="30" customWidth="1" style="21" min="2" max="2"/>
-    <col width="100" customWidth="1" style="21" min="3" max="3"/>
+    <col width="10" customWidth="1" style="24" min="1" max="1"/>
+    <col width="30" customWidth="1" style="24" min="2" max="2"/>
+    <col width="100" customWidth="1" style="24" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="21">
-      <c r="A1" s="20" t="inlineStr">
+    <row r="1" ht="18" customHeight="1" s="24">
+      <c r="A1" s="25" t="inlineStr">
         <is>
           <t>04 · Modos de investigar</t>
         </is>
@@ -6915,26 +6917,25 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" style="21" min="1" max="1"/>
-    <col width="20" customWidth="1" style="21" min="2" max="2"/>
-    <col width="100" customWidth="1" style="21" min="3" max="3"/>
+    <col width="10" customWidth="1" style="24" min="1" max="1"/>
+    <col width="20" customWidth="1" style="24" min="2" max="2"/>
+    <col width="100" customWidth="1" style="24" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="21">
-      <c r="A1" s="20" t="inlineStr">
+    <row r="1" ht="18" customHeight="1" s="24">
+      <c r="A1" s="25" t="inlineStr">
         <is>
           <t>05 · Salidas (canales de transferencia)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="22" t="inlineStr">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t>Los Laboratorios son la unidad operativa que activa las Salidas.</t>
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
@@ -7021,13 +7022,13 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" style="21" min="1" max="1"/>
-    <col width="38" customWidth="1" style="21" min="2" max="2"/>
-    <col width="100" customWidth="1" style="21" min="3" max="3"/>
+    <col width="12" customWidth="1" style="24" min="1" max="1"/>
+    <col width="38" customWidth="1" style="24" min="2" max="2"/>
+    <col width="100" customWidth="1" style="24" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="21">
-      <c r="A1" s="20" t="inlineStr">
+    <row r="1" ht="18" customHeight="1" s="24">
+      <c r="A1" s="25" t="inlineStr">
         <is>
           <t>06 · Laboratorios (grupos asociativos, nombres tentativos)</t>
         </is>
@@ -7152,28 +7153,27 @@
   <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" style="21" min="1" max="1"/>
-    <col width="28" customWidth="1" style="21" min="2" max="2"/>
-    <col width="14" customWidth="1" style="21" min="3" max="3"/>
-    <col width="60" customWidth="1" style="21" min="4" max="4"/>
-    <col width="38" customWidth="1" style="21" min="5" max="5"/>
+    <col width="10" customWidth="1" style="24" min="1" max="1"/>
+    <col width="28" customWidth="1" style="24" min="2" max="2"/>
+    <col width="14" customWidth="1" style="24" min="3" max="3"/>
+    <col width="60" customWidth="1" style="24" min="4" max="4"/>
+    <col width="38" customWidth="1" style="24" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="21">
-      <c r="A1" s="20" t="inlineStr">
+    <row r="1" ht="18" customHeight="1" s="24">
+      <c r="A1" s="25" t="inlineStr">
         <is>
           <t>07 · Investigadores (cuerpo académico EAD-PUCV)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="22" t="inlineStr">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t>Área principal es lectura — un investigador puede operar en varias. Profundización en 12_Investigador_Lab y 13_Investigador_Modo.</t>
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
           <t>INV-UEC</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>Ursula Exss Cid</t>
         </is>
@@ -7234,7 +7234,7 @@
           <t>INV-KEC</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>Katherine Exss Cid</t>
         </is>
@@ -7261,7 +7261,7 @@
           <t>INV-JFH</t>
         </is>
       </c>
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>Jorge Ferrada Herrera</t>
         </is>
@@ -7288,7 +7288,7 @@
           <t>INV-AGA</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>Andrés Garcés Alzamora</t>
         </is>
@@ -7315,7 +7315,7 @@
           <t>INV-IIY</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>Iván Ivelic Yanes</t>
         </is>
@@ -7342,7 +7342,7 @@
           <t>INV-DLC</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>David Luza Cornejo</t>
         </is>
@@ -7369,7 +7369,7 @@
           <t>INV-AMT</t>
         </is>
       </c>
-      <c r="B11" s="24" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>Adriana Marín Toro</t>
         </is>
@@ -7396,7 +7396,7 @@
           <t>INV-AMJ</t>
         </is>
       </c>
-      <c r="B12" s="24" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>Álvaro Mercado Jara</t>
         </is>
@@ -7423,7 +7423,7 @@
           <t>INV-JRG</t>
         </is>
       </c>
-      <c r="B13" s="24" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>Jaime Reyes Gil</t>
         </is>
@@ -7450,7 +7450,7 @@
           <t>INV-RSV</t>
         </is>
       </c>
-      <c r="B14" s="24" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>Rodrigo Saavedra Venegas</t>
         </is>
@@ -7477,7 +7477,7 @@
           <t>INV-DSC</t>
         </is>
       </c>
-      <c r="B15" s="24" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>Daniela Salgado Cofré</t>
         </is>
@@ -7504,7 +7504,7 @@
           <t>INV-HSG</t>
         </is>
       </c>
-      <c r="B16" s="24" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>Herbert Spencer González</t>
         </is>
@@ -7531,7 +7531,7 @@
           <t>INV-ATJ</t>
         </is>
       </c>
-      <c r="B17" s="24" t="inlineStr">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>Alfred Thiers Jusan</t>
         </is>
@@ -7552,13 +7552,13 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="16" customHeight="1" s="21">
+    <row r="18" ht="16" customHeight="1" s="24">
       <c r="A18" s="8" t="inlineStr">
         <is>
           <t>INV-LHP</t>
         </is>
       </c>
-      <c r="B18" s="24" t="inlineStr">
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>Lorena Herrera Ponce</t>
         </is>
@@ -7568,7 +7568,7 @@
           <t>ECH</t>
         </is>
       </c>
-      <c r="D18" s="25" t="inlineStr">
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t>https://wiki.ead.pucv.cl/Lorena_Herrera</t>
         </is>
@@ -7585,7 +7585,7 @@
           <t>INV-JCJP</t>
         </is>
       </c>
-      <c r="B19" s="24" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>Juan Carlos Jeldes Pontio</t>
         </is>
@@ -7612,7 +7612,7 @@
           <t>INV-MWU</t>
         </is>
       </c>
-      <c r="B20" s="24" t="inlineStr">
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>Michèle Wilkomirsky Uribe</t>
         </is>
@@ -7639,7 +7639,7 @@
           <t>INV-OAC</t>
         </is>
       </c>
-      <c r="B21" s="24" t="inlineStr">
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>Óscar Andrade Castro</t>
         </is>
@@ -7660,13 +7660,13 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="16" customHeight="1" s="21">
+    <row r="22" ht="16" customHeight="1" s="24">
       <c r="A22" s="8" t="inlineStr">
         <is>
           <t>INV-AB</t>
         </is>
       </c>
-      <c r="B22" s="24" t="inlineStr">
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>Anna Braghini</t>
         </is>
@@ -7676,7 +7676,7 @@
           <t>EAA</t>
         </is>
       </c>
-      <c r="D22" s="25" t="inlineStr">
+      <c r="D22" s="21" t="inlineStr">
         <is>
           <t>https://wiki.ead.pucv.cl/Anna_Braghini</t>
         </is>
@@ -7693,7 +7693,7 @@
           <t>INV-ACJ</t>
         </is>
       </c>
-      <c r="B23" s="24" t="inlineStr">
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>Arturo Chicano Jiménez</t>
         </is>
@@ -7720,7 +7720,7 @@
           <t>INV-SAC</t>
         </is>
       </c>
-      <c r="B24" s="24" t="inlineStr">
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>Sylvia Arriagada Cordero</t>
         </is>
@@ -7747,7 +7747,7 @@
           <t>INV-MAA</t>
         </is>
       </c>
-      <c r="B25" s="24" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>Marcelo Araya Aravena</t>
         </is>
@@ -7768,7 +7768,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="16" customHeight="1" s="21">
+    <row r="26" ht="16" customHeight="1" s="24">
       <c r="A26" s="8" t="inlineStr">
         <is>
           <t>INV-EDF</t>
@@ -7784,7 +7784,7 @@
           <t>ECH</t>
         </is>
       </c>
-      <c r="D26" s="25" t="inlineStr">
+      <c r="D26" s="21" t="inlineStr">
         <is>
           <t>https://wiki.ead.pucv.cl/Emanuela_Di_Felice</t>
         </is>
@@ -7818,38 +7818,37 @@
   <dimension ref="A1:C158"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" style="21" min="1" max="1"/>
-    <col width="28" customWidth="1" style="21" min="2" max="2"/>
-    <col width="80" customWidth="1" style="21" min="3" max="3"/>
+    <col width="50" customWidth="1" style="24" min="1" max="1"/>
+    <col width="28" customWidth="1" style="24" min="2" max="2"/>
+    <col width="80" customWidth="1" style="24" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="21">
-      <c r="A1" s="3" t="inlineStr">
+    <row r="1" ht="18" customHeight="1" s="24">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>08 · Temas (sublínea ↔ investigador ↔ tema)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="26" t="inlineStr">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>Cada fila atribuye un tema concreto a una sublínea y un investigador. Editado a mano: usa los desplegables para elegir sublínea e investigador.</t>
         </is>
       </c>
     </row>
-    <row r="3"/>
-    <row r="4" ht="30" customHeight="1" s="21">
-      <c r="A4" s="27" t="inlineStr">
+    <row r="4" ht="30" customHeight="1" s="24">
+      <c r="A4" s="22" t="inlineStr">
         <is>
           <t>sublínea</t>
         </is>
       </c>
-      <c r="B4" s="27" t="inlineStr">
+      <c r="B4" s="22" t="inlineStr">
         <is>
           <t>investigador</t>
         </is>
       </c>
-      <c r="C4" s="27" t="inlineStr">
+      <c r="C4" s="22" t="inlineStr">
         <is>
           <t>tema</t>
         </is>
@@ -10480,10 +10479,10 @@
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="A5:A505" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Nombre no válido" error="El valor debe coincidir con un nombre existente en la hoja correspondiente. Usa el menú desplegable para elegir uno." type="list">
-      <formula1>=SublineaNombres</formula1>
+      <formula1>SublineaNombres</formula1>
     </dataValidation>
     <dataValidation sqref="B5:B505" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Nombre no válido" error="El valor debe coincidir con un nombre existente en la hoja correspondiente. Usa el menú desplegable para elegir uno." type="list">
-      <formula1>=InvestigadorNombres</formula1>
+      <formula1>InvestigadorNombres</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/mad-map-data-v2.xlsx
+++ b/mad-map-data-v2.xlsx
@@ -646,7 +646,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="16" customHeight="1" s="24">
       <c r="A4" s="26" t="inlineStr">
         <is>
@@ -750,7 +749,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14" ht="16" customHeight="1" s="24">
       <c r="A14" s="26" t="inlineStr">
         <is>
@@ -2912,7 +2910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E90"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="24" min="1" max="1"/>
@@ -7150,7 +7148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" style="24" min="1" max="1"/>
@@ -7170,7 +7168,7 @@
     <row r="2">
       <c r="A2" s="23" t="inlineStr">
         <is>
-          <t>Área principal es lectura — un investigador puede operar en varias. Profundización en 12_Investigador_Lab y 13_Investigador_Modo.</t>
+          <t>Área principal es lectura — un investigador puede operar en varias. área_secundaria: segunda área autodeclarada (formulario 2024). perfil_anid desde formulario 2024; orcid y google_scholar: pendiente completar. Nota: URL ANID de Di Felice en formulario era inválida — celda vacía, pendiente corregir.</t>
         </is>
       </c>
     </row>
@@ -7192,10 +7190,30 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>área_secundaria</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
           <t>perfil_casiopea</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>perfil_anid</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>perfil_orcid</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>perfil_google_scholar</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>estado_perfil</t>
         </is>
@@ -7217,12 +7235,18 @@
           <t>EAA</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>https://wiki.ead.pucv.cl/Ursula_Exss</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>https://investigadores.anid.cl/es/public_search/researcher?id=38268</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>consolidado Casiopea + ANID</t>
         </is>
@@ -7244,12 +7268,18 @@
           <t>FCT</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>https://wiki.ead.pucv.cl/Katherine_Exss</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>https://investigadores.anid.cl/es/public_search/researcher?id=39442</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>consolidado Casiopea + ANID</t>
         </is>
@@ -7271,12 +7301,13 @@
           <t>ECH</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>https://wiki.ead.pucv.cl/Jorge_Ferrada</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>bio + cursos + proyectos + tesis</t>
         </is>
@@ -7300,10 +7331,15 @@
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
+          <t>FCT</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
           <t>https://wiki.ead.pucv.cl/Andr%C3%A9s_Garc%C3%A9s</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>línea explícita</t>
         </is>
@@ -7325,12 +7361,13 @@
           <t>ECH</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D9" s="8" t="n"/>
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>https://wiki.ead.pucv.cl/Iv%C3%A1n_Ivelic</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>línea explícita + lectura detallada</t>
         </is>
@@ -7352,12 +7389,13 @@
           <t>ECH</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>https://wiki.ead.pucv.cl/David_Luza</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>consolidado Casiopea + ANID</t>
         </is>
@@ -7379,12 +7417,13 @@
           <t>ECH</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>https://wiki.ead.pucv.cl/Adriana_Mar%C3%ADn</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>líneas explícitas</t>
         </is>
@@ -7406,12 +7445,13 @@
           <t>ECH</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>https://wiki.ead.pucv.cl/%C3%81lvaro_Mercado</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>líneas explícitas</t>
         </is>
@@ -7433,12 +7473,18 @@
           <t>EAA</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>https://wiki.ead.pucv.cl/Jaime_Reyes</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>https://investigadores.anid.cl/es/public_search/researcher?id=44715</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
         <is>
           <t>tema/área explícita</t>
         </is>
@@ -7460,12 +7506,18 @@
           <t>EAA</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>https://wiki.ead.pucv.cl/Rodrigo_Saavedra</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>https://investigadores.anid.cl/es/public_search/researcher?id=36228</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
         <is>
           <t>líneas explícitas</t>
         </is>
@@ -7489,10 +7541,20 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
+          <t>ECH</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
           <t>https://wiki.ead.pucv.cl/Daniela_Salgado</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>https://investigadores.anid.cl/es/public_search/researcher?id=43532</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
         <is>
           <t>líneas explícitas</t>
         </is>
@@ -7514,12 +7576,18 @@
           <t>FCT</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>https://wiki.ead.pucv.cl/Herbert_Spencer</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>https://investigadores.anid.cl/es/public_search/researcher?id=6662</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
         <is>
           <t>líneas explícitas</t>
         </is>
@@ -7541,12 +7609,13 @@
           <t>ECH</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D17" s="8" t="n"/>
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>https://wiki.ead.pucv.cl/Alfred_Thiers</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>líneas explícitas</t>
         </is>
@@ -7568,12 +7637,13 @@
           <t>ECH</t>
         </is>
       </c>
-      <c r="D18" s="21" t="inlineStr">
+      <c r="D18" s="21" t="n"/>
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t>https://wiki.ead.pucv.cl/Lorena_Herrera</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>ANID</t>
         </is>
@@ -7595,12 +7665,13 @@
           <t>FCT</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D19" s="8" t="n"/>
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>https://wiki.ead.pucv.cl/Juan_Carlos_Jeldes</t>
         </is>
       </c>
-      <c r="E19" s="8" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>lectura detallada de perfil</t>
         </is>
@@ -7622,12 +7693,13 @@
           <t>EAA</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="8" t="inlineStr">
         <is>
           <t>https://wiki.ead.pucv.cl/Mich%C3%A8le_Wilkomirsky</t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>ANID</t>
         </is>
@@ -7651,10 +7723,20 @@
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
+          <t>ECH</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
           <t>https://wiki.ead.pucv.cl/%C3%93scar_Andrade</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>https://investigadores.anid.cl/es/public_search/researcher?id=41600</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
         <is>
           <t>ANID</t>
         </is>
@@ -7678,10 +7760,20 @@
       </c>
       <c r="D22" s="21" t="inlineStr">
         <is>
+          <t>ECH</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
           <t>https://wiki.ead.pucv.cl/Anna_Braghini</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>https://investigadores.anid.cl/es/people/49354-Anna_Braghini</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
         <is>
           <t>deducción razonable</t>
         </is>
@@ -7703,12 +7795,13 @@
           <t>FCT</t>
         </is>
       </c>
-      <c r="D23" s="8" t="inlineStr">
+      <c r="D23" s="8" t="n"/>
+      <c r="E23" s="8" t="inlineStr">
         <is>
           <t>https://wiki.ead.pucv.cl/Arturo_Chicano</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>lectura detallada de perfil</t>
         </is>
@@ -7730,12 +7823,13 @@
           <t>FCT</t>
         </is>
       </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="8" t="inlineStr">
         <is>
           <t>https://wiki.ead.pucv.cl/Sylvia_Arriagada</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>línea explícita + lectura detallada</t>
         </is>
@@ -7757,12 +7851,13 @@
           <t>FCT</t>
         </is>
       </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="D25" s="8" t="n"/>
+      <c r="E25" s="8" t="inlineStr">
         <is>
           <t>https://wiki.ead.pucv.cl/Marcelo_Araya</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>deducción fundada</t>
         </is>
@@ -7786,10 +7881,15 @@
       </c>
       <c r="D26" s="21" t="inlineStr">
         <is>
+          <t>EAA</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
           <t>https://wiki.ead.pucv.cl/Emanuela_Di_Felice</t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>consolidado por lectura detallada</t>
         </is>
@@ -7797,8 +7897,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId1"/>

--- a/mad-map-data-v2.xlsx
+++ b/mad-map-data-v2.xlsx
@@ -7168,7 +7168,7 @@
     <row r="2">
       <c r="A2" s="23" t="inlineStr">
         <is>
-          <t>Área principal es lectura — un investigador puede operar en varias. área_secundaria: segunda área autodeclarada (formulario 2024). perfil_anid desde formulario 2024; orcid y google_scholar: pendiente completar. Nota: URL ANID de Di Felice en formulario era inválida — celda vacía, pendiente corregir.</t>
+          <t>Área principal es lectura — un investigador puede operar en varias. área_secundaria: segunda área autodeclarada (formulario 2024). perfil_anid desde formulario 2024; orcid y google_scholar: pendiente completar. Nota: URL ANID de Emanuela Di Felice en formulario era inválida — vacía, pendiente corregir.</t>
         </is>
       </c>
     </row>
@@ -7193,7 +7193,7 @@
           <t>área_secundaria</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>perfil_casiopea</t>
         </is>
@@ -7235,8 +7235,7 @@
           <t>EAA</t>
         </is>
       </c>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>https://wiki.ead.pucv.cl/Ursula_Exss</t>
         </is>
@@ -7268,8 +7267,7 @@
           <t>FCT</t>
         </is>
       </c>
-      <c r="D6" s="8" t="n"/>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>https://wiki.ead.pucv.cl/Katherine_Exss</t>
         </is>
@@ -7301,8 +7299,7 @@
           <t>ECH</t>
         </is>
       </c>
-      <c r="D7" s="8" t="n"/>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>https://wiki.ead.pucv.cl/Jorge_Ferrada</t>
         </is>
@@ -7329,12 +7326,12 @@
           <t>ECH</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>FCT</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>https://wiki.ead.pucv.cl/Andr%C3%A9s_Garc%C3%A9s</t>
         </is>
@@ -7361,8 +7358,7 @@
           <t>ECH</t>
         </is>
       </c>
-      <c r="D9" s="8" t="n"/>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>https://wiki.ead.pucv.cl/Iv%C3%A1n_Ivelic</t>
         </is>
@@ -7389,8 +7385,7 @@
           <t>ECH</t>
         </is>
       </c>
-      <c r="D10" s="8" t="n"/>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>https://wiki.ead.pucv.cl/David_Luza</t>
         </is>
@@ -7417,8 +7412,7 @@
           <t>ECH</t>
         </is>
       </c>
-      <c r="D11" s="8" t="n"/>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>https://wiki.ead.pucv.cl/Adriana_Mar%C3%ADn</t>
         </is>
@@ -7445,8 +7439,7 @@
           <t>ECH</t>
         </is>
       </c>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>https://wiki.ead.pucv.cl/%C3%81lvaro_Mercado</t>
         </is>
@@ -7473,8 +7466,7 @@
           <t>EAA</t>
         </is>
       </c>
-      <c r="D13" s="8" t="n"/>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>https://wiki.ead.pucv.cl/Jaime_Reyes</t>
         </is>
@@ -7506,8 +7498,7 @@
           <t>EAA</t>
         </is>
       </c>
-      <c r="D14" s="8" t="n"/>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>https://wiki.ead.pucv.cl/Rodrigo_Saavedra</t>
         </is>
@@ -7539,12 +7530,12 @@
           <t>FCT</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>ECH</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>https://wiki.ead.pucv.cl/Daniela_Salgado</t>
         </is>
@@ -7576,8 +7567,7 @@
           <t>FCT</t>
         </is>
       </c>
-      <c r="D16" s="8" t="n"/>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>https://wiki.ead.pucv.cl/Herbert_Spencer</t>
         </is>
@@ -7609,8 +7599,7 @@
           <t>ECH</t>
         </is>
       </c>
-      <c r="D17" s="8" t="n"/>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>https://wiki.ead.pucv.cl/Alfred_Thiers</t>
         </is>
@@ -7637,8 +7626,7 @@
           <t>ECH</t>
         </is>
       </c>
-      <c r="D18" s="21" t="n"/>
-      <c r="E18" s="8" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>https://wiki.ead.pucv.cl/Lorena_Herrera</t>
         </is>
@@ -7665,8 +7653,7 @@
           <t>FCT</t>
         </is>
       </c>
-      <c r="D19" s="8" t="n"/>
-      <c r="E19" s="8" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>https://wiki.ead.pucv.cl/Juan_Carlos_Jeldes</t>
         </is>
@@ -7693,8 +7680,7 @@
           <t>EAA</t>
         </is>
       </c>
-      <c r="D20" s="8" t="n"/>
-      <c r="E20" s="8" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>https://wiki.ead.pucv.cl/Mich%C3%A8le_Wilkomirsky</t>
         </is>
@@ -7721,12 +7707,12 @@
           <t>EAA</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>ECH</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>https://wiki.ead.pucv.cl/%C3%93scar_Andrade</t>
         </is>
@@ -7758,12 +7744,12 @@
           <t>EAA</t>
         </is>
       </c>
-      <c r="D22" s="21" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>ECH</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>https://wiki.ead.pucv.cl/Anna_Braghini</t>
         </is>
@@ -7795,8 +7781,7 @@
           <t>FCT</t>
         </is>
       </c>
-      <c r="D23" s="8" t="n"/>
-      <c r="E23" s="8" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>https://wiki.ead.pucv.cl/Arturo_Chicano</t>
         </is>
@@ -7823,8 +7808,7 @@
           <t>FCT</t>
         </is>
       </c>
-      <c r="D24" s="8" t="n"/>
-      <c r="E24" s="8" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>https://wiki.ead.pucv.cl/Sylvia_Arriagada</t>
         </is>
@@ -7851,8 +7835,7 @@
           <t>FCT</t>
         </is>
       </c>
-      <c r="D25" s="8" t="n"/>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>https://wiki.ead.pucv.cl/Marcelo_Araya</t>
         </is>
@@ -7879,12 +7862,12 @@
           <t>ECH</t>
         </is>
       </c>
-      <c r="D26" s="21" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>EAA</t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>https://wiki.ead.pucv.cl/Emanuela_Di_Felice</t>
         </is>
@@ -7900,11 +7883,6 @@
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId3"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
